--- a/artfynd/A 54944-2024 artfynd.xlsx
+++ b/artfynd/A 54944-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>206004</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Lepus timidus</t>

--- a/artfynd/A 54944-2024 artfynd.xlsx
+++ b/artfynd/A 54944-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122457740</v>
       </c>
       <c r="B2" t="n">
-        <v>55979</v>
+        <v>55983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>206004</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 54944-2024 artfynd.xlsx
+++ b/artfynd/A 54944-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122457740</v>
       </c>
       <c r="B2" t="n">
-        <v>55983</v>
+        <v>55984</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54944-2024 artfynd.xlsx
+++ b/artfynd/A 54944-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122457740</v>
+        <v>61866394</v>
       </c>
       <c r="B2" t="n">
-        <v>56078</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Långvattnets NR, Junsele, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579117</v>
+        <v>579168</v>
       </c>
       <c r="R2" t="n">
-        <v>7069063</v>
+        <v>7069073</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västernorrland</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -745,27 +745,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Fjällsjö</t>
+          <t>Junsele</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2016-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2016-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,21 +764,134 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lennart Vessberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122457740</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>579117</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7069063</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54944-2024 artfynd.xlsx
+++ b/artfynd/A 54944-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61866394</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,8 +902,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122457740</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>